--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487128_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487128_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6502</v>
+        <v>5.603</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3034</v>
+        <v>5.283</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3468</v>
+        <v>0.32</v>
       </c>
       <c r="G2" t="n">
         <v>2.8576</v>
@@ -610,13 +610,13 @@
         <v>2.3161</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5752</v>
+        <v>-0.6223</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4581</v>
+        <v>-0.4785</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1171</v>
+        <v>-0.1438</v>
       </c>
       <c r="V2" t="n">
         <v>4.9119</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. REYES ABAD</t>
+          <t>A. GARCIA NAVALON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1405</v>
+        <v>3.9358</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4988</v>
+        <v>4.8697</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6416</v>
+        <v>-0.9339</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3429</v>
+        <v>3.0013</v>
       </c>
       <c r="H3" t="n">
-        <v>0.711</v>
+        <v>0.8985</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6319</v>
+        <v>2.1028</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2889</v>
+        <v>5.0422</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.5436</v>
+        <v>0.7452</v>
       </c>
       <c r="L3" t="n">
-        <v>2.8325</v>
+        <v>4.297</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.946</v>
+        <v>-2.0409</v>
       </c>
       <c r="N3" t="n">
-        <v>1.2547</v>
+        <v>0.1533</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.2006</v>
+        <v>-2.1942</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.193</v>
+        <v>1.158</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7021</v>
+        <v>1.158</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3688</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1229</v>
+        <v>-0.4584</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4917</v>
+        <v>-0.1167</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6217</v>
+        <v>0.3515</v>
       </c>
       <c r="W3" t="n">
-        <v>1.228</v>
+        <v>0.2859</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3937</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. GARCIA NAVALON</t>
+          <t>A. REYES ABAD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1208</v>
+        <v>2.9392</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5098</v>
+        <v>0.4582</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.389</v>
+        <v>2.481</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0013</v>
+        <v>1.3429</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8985</v>
+        <v>0.711</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1028</v>
+        <v>0.6319</v>
       </c>
       <c r="J4" t="n">
-        <v>5.0422</v>
+        <v>2.2889</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7452</v>
+        <v>-0.5436</v>
       </c>
       <c r="L4" t="n">
-        <v>4.297</v>
+        <v>2.8325</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0409</v>
+        <v>-0.946</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1533</v>
+        <v>1.2547</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.1942</v>
+        <v>-2.2006</v>
       </c>
       <c r="P4" t="n">
-        <v>1.158</v>
+        <v>-0.193</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R4" t="n">
-        <v>1.158</v>
+        <v>2.7021</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3901</v>
+        <v>0.1676</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8183</v>
+        <v>-0.1635</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5718</v>
+        <v>0.3311</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3515</v>
+        <v>1.6217</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2859</v>
+        <v>1.228</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.3937</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4596</v>
+        <v>2.0921</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9395</v>
+        <v>3.7595</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4799</v>
+        <v>-1.6673</v>
       </c>
       <c r="G5" t="n">
         <v>6.0548</v>
@@ -844,13 +844,13 @@
         <v>1.7371</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3557</v>
+        <v>-0.7231</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1752</v>
+        <v>-0.3552</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1805</v>
+        <v>-0.3679</v>
       </c>
       <c r="V5" t="n">
         <v>-3.0465</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. OTERO GONZALEZ</t>
+          <t>N. NDOYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2359</v>
+        <v>0.1823</v>
       </c>
       <c r="E6" t="n">
-        <v>1.101</v>
+        <v>-0.8861</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8651</v>
+        <v>1.0684</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.142</v>
+        <v>0.0147</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7286</v>
+        <v>0.7245</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4134</v>
+        <v>-0.7097</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3182</v>
+        <v>0.2544</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1955</v>
+        <v>0.0102</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5137</v>
+        <v>0.2442</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4602</v>
+        <v>-0.2397</v>
       </c>
       <c r="N6" t="n">
-        <v>0.467</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.9272</v>
+        <v>-0.9539</v>
       </c>
       <c r="P6" t="n">
-        <v>0.579</v>
+        <v>-0.193</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.965</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5441</v>
+        <v>0.772</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2089</v>
+        <v>0.3606</v>
       </c>
       <c r="T6" t="n">
-        <v>0.234</v>
+        <v>-0.1755</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4429</v>
+        <v>0.536</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0077</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. NDOYE</t>
+          <t>J. OTERO GONZALEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1496</v>
+        <v>0.1814</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1865</v>
+        <v>0.7788</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3361</v>
+        <v>-0.5974</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0147</v>
+        <v>-1.142</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7245</v>
+        <v>-0.7286</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7097</v>
+        <v>-0.4134</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2544</v>
+        <v>0.3182</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0102</v>
+        <v>-1.1955</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2442</v>
+        <v>1.5137</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2397</v>
+        <v>-1.4602</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.467</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9539</v>
+        <v>-1.9272</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.193</v>
+        <v>0.579</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>0.772</v>
+        <v>1.5441</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3278</v>
+        <v>-0.2634</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4759</v>
+        <v>-0.0882</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8037</v>
+        <v>-0.1752</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.0077</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5061</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6077</v>
+        <v>-0.8545</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1966</v>
+        <v>-0.497</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4111</v>
+        <v>-0.3576</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0396</v>
@@ -1078,13 +1078,13 @@
         <v>0.386</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3318</v>
+        <v>0.0849</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4297</v>
+        <v>0.1292</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0978</v>
+        <v>-0.0443</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2859</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0012</v>
+        <v>-1.8019</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4693</v>
+        <v>-1.1093</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5319</v>
+        <v>-0.6926</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8895999999999999</v>
@@ -1156,13 +1156,13 @@
         <v>1.158</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0767</v>
+        <v>0.1226</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5949</v>
+        <v>-0.235</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5182</v>
+        <v>0.3576</v>
       </c>
       <c r="V9" t="n">
         <v>-1.228</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5463</v>
+        <v>-4.0212</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.991</v>
+        <v>-1.573</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5553</v>
+        <v>-2.4483</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5133</v>
@@ -1234,13 +1234,13 @@
         <v>0.579</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.033</v>
+        <v>-0.508</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7998</v>
+        <v>0.2178</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8329</v>
+        <v>-0.7258</v>
       </c>
       <c r="V10" t="n">
         <v>-0.614</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1267</v>
+        <v>-4.8892</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5573</v>
+        <v>-3.2394</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5695</v>
+        <v>-1.6498</v>
       </c>
       <c r="G11" t="n">
         <v>-4.6813</v>
@@ -1312,13 +1312,13 @@
         <v>2.1231</v>
       </c>
       <c r="S11" t="n">
-        <v>0.273</v>
+        <v>-0.4895</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7827</v>
+        <v>0.1005</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5097</v>
+        <v>-0.59</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8764999999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.474699999999999</v>
+        <v>3.367</v>
       </c>
       <c r="E12" t="n">
-        <v>6.9518</v>
+        <v>7.8444</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.4773</v>
+        <v>-4.4775</v>
       </c>
       <c r="G12" t="n">
         <v>3.005500000000001</v>
@@ -1381,7 +1381,7 @@
         <v>-17.1724</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9648999999999995</v>
+        <v>0.9648999999999996</v>
       </c>
       <c r="Q12" t="n">
         <v>-13.5104</v>
@@ -1390,13 +1390,13 @@
         <v>14.4755</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.3382</v>
+        <v>-2.4457</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.3991</v>
+        <v>-1.5068</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9391</v>
+        <v>-0.9390000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>1.8419</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. MENDEZ MADERA</t>
+          <t>R. CARTÓN CHARFOLE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.1852</v>
+        <v>2.3784</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5099</v>
+        <v>3.4</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6754</v>
+        <v>-1.0216</v>
       </c>
       <c r="G13" t="n">
-        <v>1.6825</v>
+        <v>1.3589</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2825</v>
+        <v>-0.5018</v>
       </c>
       <c r="I13" t="n">
-        <v>1.965</v>
+        <v>1.8607</v>
       </c>
       <c r="J13" t="n">
-        <v>2.3297</v>
+        <v>3.8798</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3519</v>
+        <v>-0.7349</v>
       </c>
       <c r="L13" t="n">
-        <v>1.9778</v>
+        <v>4.6147</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6473</v>
+        <v>-2.5209</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6344</v>
+        <v>0.2331</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0129</v>
+        <v>-2.754</v>
       </c>
       <c r="P13" t="n">
-        <v>0.193</v>
+        <v>2.7021</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.158</v>
+        <v>2.7021</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0239</v>
+        <v>0.4452</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8593</v>
+        <v>-0.4798</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1646</v>
+        <v>0.925</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2859</v>
+        <v>-2.1278</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-2.1278</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. TSULAIA</t>
+          <t>M. MENDEZ MADERA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9092</v>
+        <v>2.3504</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4288</v>
+        <v>1.8089</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5196</v>
+        <v>0.5415</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4283</v>
+        <v>1.6825</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.0008</v>
+        <v>-0.2825</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4291</v>
+        <v>1.965</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2098</v>
+        <v>2.3297</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.9669</v>
+        <v>0.3519</v>
       </c>
       <c r="L14" t="n">
-        <v>5.1767</v>
+        <v>1.9778</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.7815</v>
+        <v>-0.6473</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0339</v>
+        <v>-0.6344</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.7476</v>
+        <v>-0.0129</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.7371</v>
+        <v>0.193</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.8602</v>
+        <v>-0.965</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1231</v>
+        <v>1.158</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.852</v>
+        <v>0.189</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1765</v>
+        <v>0.1583</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3245</v>
+        <v>0.0307</v>
       </c>
       <c r="V14" t="n">
-        <v>3.0699</v>
+        <v>0.2859</v>
       </c>
       <c r="W14" t="n">
-        <v>4.2556</v>
+        <v>0.2859</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.1857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. CARTÓN CHARFOLE</t>
+          <t>G. TSULAIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5894</v>
+        <v>2.1244</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7977</v>
+        <v>3.4302</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2083</v>
+        <v>-1.3058</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3589</v>
+        <v>0.4283</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5018</v>
+        <v>-2.0008</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8607</v>
+        <v>2.4291</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8798</v>
+        <v>3.2098</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7349</v>
+        <v>-1.9669</v>
       </c>
       <c r="L15" t="n">
-        <v>4.6147</v>
+        <v>5.1767</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5209</v>
+        <v>-2.7815</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2331</v>
+        <v>-0.0339</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.754</v>
+        <v>-2.7476</v>
       </c>
       <c r="P15" t="n">
-        <v>2.7021</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.8602</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7021</v>
+        <v>2.1231</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3438</v>
+        <v>0.3632</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.0821</v>
+        <v>-0.1751</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7383</v>
+        <v>0.5383</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.1278</v>
+        <v>3.0699</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>4.2556</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.1278</v>
+        <v>-1.1857</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. RIVERA MOTA</t>
+          <t>A. FRECHILLA GOMEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2007</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5857</v>
+        <v>2.0599</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7864</v>
+        <v>-1.4315</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.038</v>
+        <v>1.3045</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.6913</v>
+        <v>2.4034</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.3466</v>
+        <v>-1.0989</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.0099</v>
+        <v>4.0055</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.0848</v>
+        <v>1.8163</v>
       </c>
       <c r="L16" t="n">
-        <v>2.075</v>
+        <v>2.1892</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.0281</v>
+        <v>-2.701</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3935</v>
+        <v>0.5871</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.4216</v>
+        <v>-3.2881</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0.193</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9301</v>
+        <v>2.1231</v>
       </c>
       <c r="S16" t="n">
-        <v>2.9375</v>
+        <v>0.3589</v>
       </c>
       <c r="T16" t="n">
-        <v>2.34</v>
+        <v>-0.0155</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5975</v>
+        <v>0.3744</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8999</v>
+        <v>-1.228</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1857</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2859</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. FRECHILLA GOMEZ</t>
+          <t>C. RIVERA MOTA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3558</v>
+        <v>-1.5692</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9584</v>
+        <v>-0.9164</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3142</v>
+        <v>-0.6529</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3045</v>
+        <v>-4.038</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4034</v>
+        <v>-2.6913</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0989</v>
+        <v>-1.3466</v>
       </c>
       <c r="J17" t="n">
-        <v>4.0055</v>
+        <v>-1.0099</v>
       </c>
       <c r="K17" t="n">
-        <v>1.8163</v>
+        <v>-3.0848</v>
       </c>
       <c r="L17" t="n">
-        <v>2.1892</v>
+        <v>2.075</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.701</v>
+        <v>-3.0281</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5871</v>
+        <v>0.3935</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.2881</v>
+        <v>-3.4216</v>
       </c>
       <c r="P17" t="n">
-        <v>0.193</v>
+        <v>-0</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1231</v>
+        <v>1.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6254</v>
+        <v>1.5689</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.117</v>
+        <v>0.8379</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5083</v>
+        <v>0.731</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.228</v>
+        <v>0.8999</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1857</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.228</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. CAMPBELL</t>
+          <t>D. MERKVILADZE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.7321</v>
+        <v>-2.1358</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-2.3712</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.901</v>
+        <v>0.2353</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.2109</v>
+        <v>0.469</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7029</v>
+        <v>-0.5971</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.508</v>
+        <v>1.066</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2294</v>
+        <v>0.8154</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0095</v>
+        <v>-0.5434</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.2199</v>
+        <v>1.3588</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.9815</v>
+        <v>-0.3464</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3066</v>
+        <v>-0.0537</v>
       </c>
       <c r="O18" t="n">
-        <v>-3.2881</v>
+        <v>-0.2928</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.965</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.8951</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9301</v>
+        <v>1.5441</v>
       </c>
       <c r="S18" t="n">
-        <v>3.6718</v>
+        <v>0.2601</v>
       </c>
       <c r="T18" t="n">
-        <v>3.0076</v>
+        <v>-0.2915</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6642</v>
+        <v>0.5516</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.228</v>
+        <v>-1.5138</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>-1.5138</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. MERKVILADZE</t>
+          <t>S. CAMPBELL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.8699</v>
+        <v>-4.916</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.972</v>
+        <v>-2.934</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1022</v>
+        <v>-1.982</v>
       </c>
       <c r="G19" t="n">
-        <v>0.469</v>
+        <v>-4.2109</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5971</v>
+        <v>-0.7029</v>
       </c>
       <c r="I19" t="n">
-        <v>1.066</v>
+        <v>-3.508</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8154</v>
+        <v>-1.2294</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5434</v>
+        <v>-1.0095</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3588</v>
+        <v>-0.2199</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3464</v>
+        <v>-2.9815</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0537</v>
+        <v>0.3066</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2928</v>
+        <v>-3.2881</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3511</v>
+        <v>-0.965</v>
       </c>
       <c r="Q19" t="n">
         <v>-2.8951</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5441</v>
+        <v>1.9301</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4739</v>
+        <v>1.4879</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8923</v>
+        <v>0.9046</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4184</v>
+        <v>0.5833</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.5138</v>
+        <v>-1.228</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X19" t="n">
         <v>-1.5138</v>
@@ -1969,22 +1969,22 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.474699999999999</v>
+        <v>-1.139300000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>4.477399999999999</v>
+        <v>4.477399999999998</v>
       </c>
       <c r="F20" t="n">
-        <v>-6.9519</v>
+        <v>-5.617</v>
       </c>
       <c r="G20" t="n">
         <v>-3.0057</v>
       </c>
       <c r="H20" t="n">
-        <v>-4.373</v>
+        <v>-4.372999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>1.367299999999999</v>
+        <v>1.367300000000001</v>
       </c>
       <c r="J20" t="n">
         <v>12.0009</v>
@@ -1999,7 +1999,7 @@
         <v>-15.0067</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7982999999999999</v>
+        <v>0.7983</v>
       </c>
       <c r="O20" t="n">
         <v>-15.8051</v>
@@ -2014,13 +2014,13 @@
         <v>13.5106</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3381</v>
+        <v>4.6732</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9389999999999997</v>
+        <v>0.9389</v>
       </c>
       <c r="U20" t="n">
-        <v>2.3992</v>
+        <v>3.7343</v>
       </c>
       <c r="V20" t="n">
         <v>-1.8419</v>
